--- a/test/project/xlsx/PostProcess.xlsx
+++ b/test/project/xlsx/PostProcess.xlsx
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yongheekim\.julia\dev\GameDataManager\test\project\xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1AA44497-C0A6-4CE4-BFD2-728E1DB79821}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7A188CD-AC99-4BB4-BF81-33269648A2F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1920" yWindow="1920" windowWidth="30960" windowHeight="12660" xr2:uid="{52D9C27D-0EF6-DD41-9728-0267E68F7539}"/>
+    <workbookView xWindow="41172" yWindow="-108" windowWidth="30936" windowHeight="17496" xr2:uid="{52D9C27D-0EF6-DD41-9728-0267E68F7539}"/>
   </bookViews>
   <sheets>
     <sheet name="OmitNull" sheetId="1" r:id="rId1"/>
     <sheet name="EmptyValue" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr fullCalcOnLoad="1" calcMode="auto"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -26,20 +26,14 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="12">
   <si>
     <t>/Key</t>
   </si>
   <si>
-    <t>/ExpectedReward/1/GameplayTag</t>
-  </si>
-  <si>
     <t>/ExpectedReward/1/Count</t>
   </si>
   <si>
-    <t>/ExpectedReward/2/GameplayTag</t>
-  </si>
-  <si>
     <t>/ExpectedReward/2/Count</t>
   </si>
   <si>
@@ -64,13 +58,10 @@
     <t>Third</t>
   </si>
   <si>
-    <t>/ExpectedReward</t>
-  </si>
-  <si>
-    <t>{"GameplayTag":Id.Loot.A;"Count":1};{"GameplayTag":Id.Loot.B;"Count":2}</t>
-  </si>
-  <si>
-    <t>{"GameplayTag":Id.Loot.X;"Count":5}</t>
+    <t>/ExpectedReward/2/Id</t>
+  </si>
+  <si>
+    <t>/ExpectedReward/1/Id</t>
   </si>
 </sst>
 </file>
@@ -422,70 +413,62 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{81BA9082-25CC-4FD5-95A1-FD8549C8C1F1}">
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:E4"/>
   <sheetFormatPr defaultColWidth="11.19921875" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="C2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2">
-        <v>1</v>
-      </c>
-      <c r="B2" t="s">
+      <c r="E2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
         <v>5</v>
       </c>
-      <c r="C2">
-        <v>1</v>
-      </c>
-      <c r="D2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E2">
-        <v>2</v>
-      </c>
-      <c r="F2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A3">
-        <v>2</v>
-      </c>
-      <c r="B3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C3">
+      <c r="C3" t="n">
         <v>5</v>
       </c>
-      <c r="F3" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A4">
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4" t="n">
         <v>3</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -499,39 +482,39 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
         <v>8</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C2" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A2">
-        <v>1</v>
-      </c>
-      <c r="B2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C2">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3">
-        <v>2</v>
-      </c>
-      <c r="C3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A4">
-        <v>3</v>
-      </c>
-      <c r="B4" t="s">
-        <v>11</v>
-      </c>
-      <c r="C4">
+      <c r="C4" t="n">
         <v>0</v>
       </c>
     </row>
